--- a/Dicionario_de_Dados_Clinica.xlsx
+++ b/Dicionario_de_Dados_Clinica.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="n"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>cpf</t>
@@ -640,15 +640,19 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>CPF da pessoa, usado tambem como identificador de unicidade</t>
+          <t>CPF da pessoa (somente numeros); valor unico por pessoa</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="n"/>
+      <c r="A4" s="6"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>nome</t>
@@ -669,7 +673,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Primeiro nome da pessoa</t>
@@ -677,7 +681,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="n"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>sobrenome</t>
@@ -698,7 +702,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Sobrenome da pessoa</t>
@@ -706,7 +710,7 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="n"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>sexo</t>
@@ -727,7 +731,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Sexo/genero informado pela pessoa</t>
@@ -735,7 +739,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="n"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>email</t>
@@ -756,7 +760,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Endereco de e-mail de contato</t>
@@ -764,7 +768,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="n"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>data_nascimento</t>
@@ -785,7 +789,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Data de nascimento da pessoa</t>
@@ -830,7 +834,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="n"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>id_pessoa</t>
@@ -863,7 +867,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="n"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>logradouro</t>
@@ -884,7 +888,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Nome da rua/avenida</t>
@@ -892,7 +896,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="n"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>numero</t>
@@ -913,7 +917,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Numero do imovel</t>
@@ -921,7 +925,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="n"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>bairro</t>
@@ -942,7 +946,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Bairro do endereco</t>
@@ -950,7 +954,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="n"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>cidade</t>
@@ -971,7 +975,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Cidade do endereco</t>
@@ -979,7 +983,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="n"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>estado</t>
@@ -1000,7 +1004,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Sigla do estado (UF)</t>
@@ -1008,7 +1012,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="6" t="n"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>cep</t>
@@ -1029,7 +1033,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Codigo de Enderecamento Postal</t>
@@ -1037,7 +1041,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="n"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>complemento</t>
@@ -1058,7 +1062,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Complemento do endereco (apto, bloco, etc.)</t>
@@ -1103,7 +1107,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="6" t="n"/>
+      <c r="A19" s="6"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>id_pessoa</t>
@@ -1136,7 +1140,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="7" t="n"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>numero</t>
@@ -1157,7 +1161,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Numero de telefone com DDD</t>
@@ -1202,7 +1206,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="6" t="n"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>id_pessoa</t>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>FK, UK</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1235,7 +1239,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="7" t="n"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>tipo_sanguineo</t>
@@ -1256,7 +1260,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="4"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Tipo sanguineo do paciente (ex.: O+, A-)</t>
@@ -1301,7 +1305,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="6" t="n"/>
+      <c r="A25" s="6"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>id_pessoa</t>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>FK, UK</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="6" t="n"/>
+      <c r="A26" s="6"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>cargo</t>
@@ -1355,7 +1359,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Cargo/funcao exercida na clinica</t>
@@ -1363,7 +1367,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="7" t="n"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>data_contratacao</t>
@@ -1384,7 +1388,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Data de contratacao do funcionario</t>
@@ -1429,7 +1433,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="6" t="n"/>
+      <c r="A29" s="6"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>id_funcionario</t>
@@ -1452,7 +1456,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>FK, UK</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1462,7 +1466,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="7" t="n"/>
+      <c r="A30" s="7"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>crm</t>
@@ -1483,10 +1487,14 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Numero de registro no Conselho Regional de Medicina</t>
+          <t>Numero de registro no Conselho Regional de Medicina; valor unico</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1536,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="7" t="n"/>
+      <c r="A32" s="7"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>nome</t>
@@ -1549,10 +1557,10 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Nome da especialidade (ex.: Cardiologia)</t>
+          <t>Nome da especialidade (ex.: Ginecologia)</t>
         </is>
       </c>
     </row>
@@ -1582,9 +1590,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="6" t="n"/>
+      <c r="A34" s="6"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
           <t>id_especialidade</t>
@@ -1615,9 +1623,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="7" t="n"/>
+      <c r="A35" s="7"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
           <t>rqe</t>
@@ -1648,7 +1656,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="F35" s="4"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Registro de Qualificacao de Especialista referente a essa combinacao</t>
@@ -1693,7 +1701,7 @@
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="7" t="n"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
           <t>descricao</t>
@@ -1714,7 +1722,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Descricao da alergia (ex.: Dipirona, Latex)</t>
@@ -1747,9 +1755,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -1759,7 +1767,7 @@
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="6" t="n"/>
+      <c r="A39" s="6"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>id_alergia</t>
@@ -1780,9 +1788,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -1792,7 +1800,7 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="6" t="n"/>
+      <c r="A40" s="6"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>gravidade</t>
@@ -1813,7 +1821,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="F40" s="4"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Gravidade da reacao alergica (leve, moderada, grave)</t>
@@ -1821,7 +1829,7 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="7" t="n"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
           <t>data_identificacao</t>
@@ -1842,7 +1850,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="F41" s="4"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Data em que a alergia foi identificada/registrada</t>
@@ -1887,7 +1895,7 @@
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="6" t="n"/>
+      <c r="A43" s="6"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>descricao</t>
@@ -1908,7 +1916,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="F43" s="4"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Descricao da doenca/condicao referente ao codigo</t>
@@ -1916,7 +1924,7 @@
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="7" t="n"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
           <t>categoria</t>
@@ -1937,7 +1945,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="F44" s="4"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Categoria/capitulo do CID a que o codigo pertence</t>
@@ -1982,7 +1990,7 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="6" t="n"/>
+      <c r="A46" s="6"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>id_paciente</t>
@@ -2005,7 +2013,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>FK</t>
+          <t>FK, UK</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2015,7 +2023,7 @@
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="6" t="n"/>
+      <c r="A47" s="6"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>data_abertura</t>
@@ -2036,7 +2044,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Data de abertura do prontuario</t>
@@ -2044,7 +2052,7 @@
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="7" t="n"/>
+      <c r="A48" s="7"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>sintomas</t>
@@ -2065,7 +2073,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="F48" s="4"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Sintomas gerais registrados na abertura do prontuario</t>
@@ -2110,7 +2118,7 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="6" t="n"/>
+      <c r="A50" s="6"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
           <t>id_prontuario</t>
@@ -2143,7 +2151,7 @@
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="6" t="n"/>
+      <c r="A51" s="6"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>id_consulta</t>
@@ -2166,158 +2174,158 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
+          <t>FK, UK</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Consulta que originou este registro (uma evolucao por consulta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="6"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Data do registro de evolucao</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="6"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>queixa_principal</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Queixa principal relatada pelo paciente na consulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="6"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>diagnostico</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Diagnostico textual do medico para a consulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="6"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>cod_cid</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Consulta que originou este registro de evolucao</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Data do registro de evolucao</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>queixa_principal</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Codigo CID associado ao diagnostico</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="7"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>conduta</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Queixa principal relatada pelo paciente na consulta</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>diagnostico</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Diagnostico textual do medico para a consulta</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>cod_cid</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Codigo CID associado ao diagnostico</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>conduta</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="F56" s="4"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Conduta/tratamento definido pelo medico</t>
@@ -2362,7 +2370,7 @@
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="6" t="n"/>
+      <c r="A58" s="6"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
           <t>nome</t>
@@ -2383,7 +2391,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="F58" s="4"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
           <t>Nome do convenio</t>
@@ -2391,7 +2399,7 @@
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="6" t="n"/>
+      <c r="A59" s="6"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>registro_ans</t>
@@ -2412,7 +2420,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="F59" s="4"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Numero de registro na ANS</t>
@@ -2420,7 +2428,7 @@
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="7" t="n"/>
+      <c r="A60" s="7"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
           <t>telefone_contato</t>
@@ -2441,7 +2449,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="F60" s="4"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Telefone de contato do convenio</t>
@@ -2449,9 +2457,9 @@
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>PACIENTE_CONVENIO</t>
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>PACIENTE_CONVENIO  (revisada)</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2474,9 +2482,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -2486,7 +2494,7 @@
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="6" t="n"/>
+      <c r="A62" s="6"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
           <t>id_convenio</t>
@@ -2507,9 +2515,9 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -2519,7 +2527,7 @@
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="6" t="n"/>
+      <c r="A63" s="6"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>numero_carteirinha</t>
@@ -2540,7 +2548,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="F63" s="4"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Numero da carteirinha do paciente no convenio</t>
@@ -2548,7 +2556,7 @@
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="6" t="n"/>
+      <c r="A64" s="6"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
           <t>data_inicio</t>
@@ -2569,7 +2577,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="F64" s="4"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
           <t>Data de inicio da vigencia do vinculo</t>
@@ -2577,7 +2585,7 @@
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="6" t="n"/>
+      <c r="A65" s="6"/>
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>data_validade</t>
@@ -2595,18 +2603,18 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F65" s="4"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Data de validade/expiracao do vinculo</t>
+          <t>Data de validade da carteirinha (obrigatoria pela regra de negocio)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="7" t="n"/>
+      <c r="A66" s="7"/>
       <c r="B66" s="3" t="inlineStr">
         <is>
           <t>ativo</t>
@@ -2627,7 +2635,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="F66" s="4"/>
       <c r="G66" s="3" t="inlineStr">
         <is>
           <t>Indica se o vinculo com o convenio esta ativo</t>
@@ -2672,7 +2680,7 @@
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="6" t="n"/>
+      <c r="A68" s="6"/>
       <c r="B68" s="3" t="inlineStr">
         <is>
           <t>numero</t>
@@ -2693,7 +2701,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="F68" s="4"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
           <t>Numero/identificacao da sala</t>
@@ -2701,7 +2709,7 @@
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="7" t="n"/>
+      <c r="A69" s="7"/>
       <c r="B69" s="3" t="inlineStr">
         <is>
           <t>andar</t>
@@ -2722,7 +2730,7 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="F69" s="4"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Andar onde a sala esta localizada</t>
@@ -2767,7 +2775,7 @@
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="n"/>
+      <c r="A71" s="6"/>
       <c r="B71" s="3" t="inlineStr">
         <is>
           <t>id_medico</t>
@@ -2800,7 +2808,7 @@
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="6" t="n"/>
+      <c r="A72" s="6"/>
       <c r="B72" s="3" t="inlineStr">
         <is>
           <t>id_sala</t>
@@ -2833,7 +2841,7 @@
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="6" t="n"/>
+      <c r="A73" s="6"/>
       <c r="B73" s="3" t="inlineStr">
         <is>
           <t>data</t>
@@ -2854,7 +2862,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="F73" s="4"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Data do horario disponivel/reservado</t>
@@ -2862,7 +2870,7 @@
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="6" t="n"/>
+      <c r="A74" s="6"/>
       <c r="B74" s="3" t="inlineStr">
         <is>
           <t>hora_inicio</t>
@@ -2883,7 +2891,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="F74" s="4"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
           <t>Horario de inicio do bloco de agenda</t>
@@ -2891,7 +2899,7 @@
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="6" t="n"/>
+      <c r="A75" s="6"/>
       <c r="B75" s="3" t="inlineStr">
         <is>
           <t>hora_fim</t>
@@ -2912,7 +2920,7 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="F75" s="4"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Horario de termino do bloco de agenda</t>
@@ -2920,7 +2928,7 @@
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="7" t="n"/>
+      <c r="A76" s="7"/>
       <c r="B76" s="3" t="inlineStr">
         <is>
           <t>status</t>
@@ -2941,17 +2949,17 @@
           <t>Nao</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="F76" s="4"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Situacao do horario (disponivel, reservado, bloqueado)</t>
+          <t>Situacao do horario (disponivel, reservado, ocupado, bloqueado)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONSULTA</t>
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>CONSULTA  (revisada)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2986,7 +2994,7 @@
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="6" t="n"/>
+      <c r="A78" s="6"/>
       <c r="B78" s="3" t="inlineStr">
         <is>
           <t>id_paciente</t>
@@ -3019,7 +3027,7 @@
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="6" t="n"/>
+      <c r="A79" s="6"/>
       <c r="B79" s="3" t="inlineStr">
         <is>
           <t>id_medico</t>
@@ -3052,7 +3060,7 @@
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="6" t="n"/>
+      <c r="A80" s="6"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
           <t>id_sala</t>
@@ -3085,7 +3093,7 @@
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="6" t="n"/>
+      <c r="A81" s="6"/>
       <c r="B81" s="3" t="inlineStr">
         <is>
           <t>id_convenio</t>
@@ -3118,1530 +3126,2024 @@
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="6" t="n"/>
+      <c r="A82" s="6"/>
       <c r="B82" s="3" t="inlineStr">
         <is>
+          <t>id_horario</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Horario da agenda ocupado pela consulta (o horario passa a ocupado ao confirmar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="6"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>data_hora</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>Data e hora agendada da consulta</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="6" t="n"/>
-      <c r="B83" s="3" t="inlineStr">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="6"/>
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>tipo_consulta</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>Tipo de consulta (primeira vez, retorno, urgencia)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="3" t="inlineStr">
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="6"/>
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>Situacao da consulta (agendada, realizada, cancelada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Situacao da consulta (agendada, confirmada, realizada, cancelada, remarcada, falta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6"/>
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>10,2</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="F86" s="4"/>
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>Valor cobrado pela consulta</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="7" t="n"/>
-      <c r="B86" s="3" t="inlineStr">
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="7"/>
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>observacoes</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="F87" s="4"/>
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>Observacoes gerais sobre a consulta</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>PAGAMENTO</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>PAGAMENTO  (revisada)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>id_pagamento</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>Identificador unico do pagamento</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="3" t="inlineStr">
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="6"/>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>id_consulta</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>Consulta a que o pagamento se refere</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="3" t="inlineStr">
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6"/>
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>10,2</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>Valor pago</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="3" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="6"/>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>forma_pagamento</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>Forma de pagamento (cartao, pix, dinheiro, etc.)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="3" t="inlineStr">
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="6"/>
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>data_pagamento</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>Data em que o pagamento foi efetuado</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="7" t="n"/>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Data em que o pagamento foi efetuado (nulo enquanto pendente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="7"/>
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>Situacao do pagamento (pago, pendente, estornado)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>MEDICAMENTO</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>id_medicamento</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>Identificador unico do medicamento</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="3" t="inlineStr">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6"/>
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>Nome comercial do medicamento</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="3" t="inlineStr">
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="6"/>
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>principio_ativo</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="F96" s="4"/>
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>Principio ativo do medicamento</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="3" t="inlineStr">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6"/>
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>fabricante</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="F97" s="4"/>
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>Fabricante/laboratorio do medicamento</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="7" t="n"/>
-      <c r="B97" s="3" t="inlineStr">
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="7"/>
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>tarja</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="F98" s="4"/>
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>Tipo de tarja (livre, amarela, vermelha, preta)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>PRESCRICAO</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>id_prescricao</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>Identificador unico da prescricao</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="6" t="n"/>
-      <c r="B99" s="3" t="inlineStr">
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="6"/>
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>id_consulta</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>Consulta que originou a prescricao</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="3" t="inlineStr">
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6"/>
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>data_emissao</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>Data de emissao da prescricao</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="7" t="n"/>
-      <c r="B101" s="3" t="inlineStr">
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="7"/>
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>validade</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="F102" s="4"/>
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>Data de validade da prescricao</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>ITEM_PRESCRICAO</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>id_prescricao</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Prescricao a que este item pertence</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="6"/>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>id_medicamento</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Medicamento prescrito neste item</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="6"/>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>posologia</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Instrucoes de uso do medicamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6"/>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>dosagem</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Dosagem prescrita</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="7"/>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>duracao_tratamento</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Duracao do tratamento com este medicamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TIPO_EXAME</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>id_tipo_exame</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do tipo de exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="6"/>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Nome do tipo de exame (ex.: Hemograma)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="6"/>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>preco_padrao</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>10,2</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Preco padrao cobrado por este tipo de exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="7"/>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>preparo_necessario</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Instrucoes de preparo previo necessario</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>LABORATORIO_EXTERNO</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>id_laboratorio</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do laboratorio externo</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="6"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Nome do laboratorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="6"/>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>cnpj</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>CNPJ do laboratorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="7"/>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>telefone</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Telefone de contato do laboratorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>EXAME</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>id_exame</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do exame solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="6"/>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>id_consulta</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>Prescricao a que este item pertence</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>id_medicamento</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Consulta que originou a solicitacao do exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="6"/>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>id_tipo_exame</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>Medicamento prescrito neste item</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>posologia</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de exame solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="6"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>id_paciente</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Paciente que realizara o exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="6"/>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>id_funcionario_responsavel</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Funcionario responsavel pela coleta/execucao</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="6"/>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>id_laboratorio_externo</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Laboratorio externo que processara o exame (se aplicavel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="6"/>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>data_solicitacao</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F122" s="4"/>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Data em que o exame foi solicitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="6"/>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>data_realizacao</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F123" s="4"/>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Data em que o exame foi efetivamente realizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="7"/>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>Instrucoes de uso do medicamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>dosagem</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F124" s="4"/>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Situacao do exame (solicitado, coletado, concluido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>RESULTADO_EXAME</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>id_resultado</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do resultado do exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="6"/>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>id_exame</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>FK, UK</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Exame ao qual este resultado pertence (um resultado por exame)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="6"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>id_medico</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Medico que assina/valida o resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="6"/>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>data_resultado</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F128" s="4"/>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Data de emissao do resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="6"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>laudo</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F129" s="4"/>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Laudo textual do resultado do exame</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="7"/>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>arquivo_anexo</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>Dosagem prescrita</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="7" t="n"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>duracao_tratamento</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="F130" s="4"/>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Caminho/referencia do arquivo anexado (PDF, imagem etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>FOLLOW_UP  (nova)</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>id_follow_up</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="6"/>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>id_consulta</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>FK, UK</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Consulta acompanhada (um follow-up por consulta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="6"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>data_prevista</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F133" s="4"/>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Data prevista do contato (padrao: 1 semana apos a consulta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="6"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>data_realizacao</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F134" s="4"/>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>Data em que o contato foi realizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="6"/>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>Duracao do tratamento com este medicamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>TIPO_EXAME</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>id_tipo_exame</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="F135" s="4"/>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Canal do contato (presencial, telefone, mensagem)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="6"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>evolucao_sintomas</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F136" s="4"/>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Como a paciente relata a evolucao dos sintomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="6"/>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>adesao_tratamento</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F137" s="4"/>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Adesao ao tratamento (total, parcial, nao iniciou)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="6"/>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>duvidas</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F138" s="4"/>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Duvidas relatadas pela paciente</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="7"/>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F139" s="4"/>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Situacao do follow-up (pendente, realizado, sem retorno)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>LEMBRETE  (nova)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>id_lembrete</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>Identificador unico do tipo de exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="6" t="n"/>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Identificador unico do lembrete</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="6"/>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>id_consulta</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Consulta a que o lembrete se refere</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="6"/>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>VARCHAR</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>Nome do tipo de exame (ex.: Hemograma)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="6" t="n"/>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>preco_padrao</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>DECIMAL</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>10,2</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F142" s="4"/>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Tipo do lembrete (aviso, confirmacao_presenca)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="6"/>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>data_envio</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F143" s="4"/>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Data e hora do envio pela IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="6"/>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+      <c r="F144" s="4"/>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Canal de envio (WhatsApp, e-mail, SMS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="7"/>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>Preco padrao cobrado por este tipo de exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="7" t="n"/>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>preparo_necessario</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>Instrucoes de preparo previo necessario</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>LABORATORIO_EXTERNO</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>id_laboratorio</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>Identificador unico do laboratorio externo</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="30" customHeight="1">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>Nome do laboratorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="30" customHeight="1">
-      <c r="A113" s="6" t="n"/>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>cnpj</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>CNPJ do laboratorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="7" t="n"/>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>telefone</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>Telefone de contato do laboratorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>EXAME</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>id_exame</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>Identificador unico do exame solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="6" t="n"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>id_consulta</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>Consulta que originou a solicitacao do exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="6" t="n"/>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>id_tipo_exame</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>Tipo de exame solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="6" t="n"/>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>id_paciente</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>Paciente que realizara o exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="30" customHeight="1">
-      <c r="A119" s="6" t="n"/>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>id_funcionario_responsavel</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>Funcionario responsavel pela coleta/execucao</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="30" customHeight="1">
-      <c r="A120" s="6" t="n"/>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>id_laboratorio_externo</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>Laboratorio externo que processara o exame (se aplicavel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="30" customHeight="1">
-      <c r="A121" s="6" t="n"/>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>data_solicitacao</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>Data em que o exame foi solicitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="6" t="n"/>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>data_realizacao</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>Data em que o exame foi efetivamente realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="7" t="n"/>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>Situacao do exame (solicitado, coletado, concluido)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>RESULTADO_EXAME</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>id_resultado</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>Identificador unico do resultado do exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="6" t="n"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>id_exame</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F125" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>Exame ao qual este resultado pertence</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="6" t="n"/>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>id_medico</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>Medico que assina/valida o resultado</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="6" t="n"/>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>data_resultado</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>Nao</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>Data de emissao do resultado</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="30" customHeight="1">
-      <c r="A128" s="6" t="n"/>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>laudo</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>Laudo textual do resultado do exame</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="30" customHeight="1">
-      <c r="A129" s="7" t="n"/>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>arquivo_anexo</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>Caminho/referencia do arquivo anexado (PDF, imagem etc.)</t>
+      <c r="F145" s="4"/>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Resposta da paciente ao lembrete de confirmacao (nulo se nao respondeu)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <mergeCells count="26">
+  <mergeCells count="28">
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A17"/>
+    <mergeCell ref="A18:A20"/>
     <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A107:A110"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A2:A8"/>
     <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A42:A44"/>
     <mergeCell ref="A45:A48"/>
     <mergeCell ref="A49:A56"/>
-    <mergeCell ref="A111:A114"/>
+    <mergeCell ref="A57:A60"/>
     <mergeCell ref="A61:A66"/>
     <mergeCell ref="A67:A69"/>
-    <mergeCell ref="A77:A86"/>
-    <mergeCell ref="A87:A92"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="A124:A129"/>
-    <mergeCell ref="A93:A97"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A9:A17"/>
-    <mergeCell ref="A57:A60"/>
     <mergeCell ref="A70:A76"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="A77:A87"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A94:A98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="A108:A111"/>
+    <mergeCell ref="A112:A115"/>
+    <mergeCell ref="A116:A124"/>
+    <mergeCell ref="A125:A130"/>
+    <mergeCell ref="A131:A139"/>
+    <mergeCell ref="A140:A145"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4653,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4709,7 +5211,7 @@
       <c r="D2" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4719,7 +5221,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Fraca</t>
+          <t>Forte</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -4730,7 +5232,11 @@
       <c r="D3" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Possui PK propria; depende de PESSOA apenas pela FK obrigatoria</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4740,7 +5246,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Fraca</t>
+          <t>Forte</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4751,7 +5257,11 @@
       <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Possui PK propria; depende de PESSOA apenas pela FK obrigatoria</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4772,10 +5282,10 @@
       <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>FUNCIONARIO</t>
         </is>
@@ -4800,7 +5310,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>MEDICO</t>
         </is>
@@ -4843,7 +5353,7 @@
       <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4864,7 +5374,7 @@
       <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4885,7 +5395,7 @@
       <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4906,10 +5416,10 @@
       <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>CID</t>
         </is>
@@ -4952,10 +5462,10 @@
       <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>EVOLUCAO_PRONTUARIO</t>
         </is>
@@ -4998,7 +5508,7 @@
       <c r="D15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -5019,7 +5529,11 @@
       <c r="D16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>data_validade passou a ser obrigatoria (regra de negocio)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -5040,7 +5554,7 @@
       <c r="D17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -5061,7 +5575,7 @@
       <c r="D18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -5080,9 +5594,13 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Nova FK id_horario (AGENDA): liga a consulta ao horario ocupado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -5103,7 +5621,11 @@
       <c r="D20" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>data_pagamento passou a aceitar nulo (pagamento pendente)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -5124,7 +5646,7 @@
       <c r="D21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -5145,7 +5667,7 @@
       <c r="D22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5166,7 +5688,7 @@
       <c r="D23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5187,7 +5709,7 @@
       <c r="D24" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5208,7 +5730,7 @@
       <c r="D25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5229,7 +5751,7 @@
       <c r="D26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5250,7 +5772,57 @@
       <c r="D27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>FOLLOW_UP</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>id_follow_up</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Entidade nova: registra o acompanhamento 1 semana apos a consulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>LEMBRETE</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Forte</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>id_lembrete</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Entidade nova: registra os 3 lembretes e a confirmacao de presenca</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
